--- a/data/trans_camb/P8_2_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P8_2_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,57</t>
+          <t>-2,56; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,11</t>
+          <t>-3,46; -0,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,43</t>
+          <t>-2,89; 2,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,58</t>
+          <t>-1,48; 3,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,42</t>
+          <t>-1,47; 3,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,45</t>
+          <t>-2,75; 2,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,8</t>
+          <t>-1,37; 1,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,96</t>
+          <t>-2,14; 0,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,41</t>
+          <t>-2,25; 1,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 98,04</t>
+          <t>-70,95; 92,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,87</t>
+          <t>-100,0; 17,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,5</t>
+          <t>-100,0; 195,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 228,07</t>
+          <t>-44,24; 187,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 212,04</t>
+          <t>-45,63; 195,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 175,72</t>
+          <t>-84,54; 159,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 98,1</t>
+          <t>-39,84; 86,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 55,75</t>
+          <t>-62,1; 45,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,31; 70,66</t>
+          <t>-73,61; 101,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,96</t>
+          <t>-1,1; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,59</t>
+          <t>-2,22; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,04</t>
+          <t>-1,74; 3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,3</t>
+          <t>-3,9; 1,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,09</t>
+          <t>-4,27; 1,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -2,38</t>
+          <t>-6,95; -2,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,44</t>
+          <t>-1,6; 1,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,92</t>
+          <t>-2,2; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,32</t>
+          <t>-3,55; -0,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 134,73</t>
+          <t>-26,9; 136,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 74,71</t>
+          <t>-56,98; 67,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 135,39</t>
+          <t>-47,76; 142,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 29,99</t>
+          <t>-55,1; 27,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 28,76</t>
+          <t>-58,19; 28,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,55; -51,22</t>
+          <t>-92,64; -48,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 41,55</t>
+          <t>-32,06; 46,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 26,91</t>
+          <t>-44,46; 26,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,39; -7,5</t>
+          <t>-71,63; -1,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,28</t>
+          <t>-1,97; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,73</t>
+          <t>-2,01; 3,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,32</t>
+          <t>-1,95; 3,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,57</t>
+          <t>0,42; 6,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,85</t>
+          <t>-2,79; 2,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,96</t>
+          <t>-3,56; 2,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,11</t>
+          <t>-0,03; 4,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,09</t>
+          <t>-1,74; 2,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,91</t>
+          <t>-2,08; 1,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 85,26</t>
+          <t>-31,14; 74,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 75,23</t>
+          <t>-31,94; 82,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 91,53</t>
+          <t>-32,82; 87,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 111,19</t>
+          <t>4,54; 105,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 48,75</t>
+          <t>-31,61; 49,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 33,05</t>
+          <t>-41,14; 37,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 78,09</t>
+          <t>-0,74; 77,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 41,34</t>
+          <t>-24,65; 41,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 35,02</t>
+          <t>-29,15; 36,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,65</t>
+          <t>-3,01; 4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,9</t>
+          <t>-1,39; 6,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 63,43</t>
+          <t>0,11; 62,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 5,27</t>
+          <t>-3,77; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,83</t>
+          <t>-5,62; 2,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,06</t>
+          <t>-7,96; 0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,53</t>
+          <t>-2,2; 3,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 3,18</t>
+          <t>-2,49; 3,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 42,82</t>
+          <t>-1,92; 39,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 58,88</t>
+          <t>-26,26; 59,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 75,96</t>
+          <t>-12,29; 80,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 837,15</t>
+          <t>0,07; 744,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 36,74</t>
+          <t>-21,1; 37,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 20,53</t>
+          <t>-29,97; 19,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 0,51</t>
+          <t>-41,91; 3,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 31,12</t>
+          <t>-14,81; 32,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 27,88</t>
+          <t>-16,98; 27,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 344,07</t>
+          <t>-14,01; 353,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 1,98</t>
+          <t>-9,89; 1,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 1,25</t>
+          <t>-10,31; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 1,77</t>
+          <t>-8,92; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 12,33</t>
+          <t>-0,66; 12,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 7,19</t>
+          <t>-5,33; 7,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,56; -0,56</t>
+          <t>-10,99; 0,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,33</t>
+          <t>-3,74; 5,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,87</t>
+          <t>-5,77; 3,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -0,61</t>
+          <t>-8,15; -0,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 9,31</t>
+          <t>-36,22; 7,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 6,0</t>
+          <t>-35,67; 7,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 8,17</t>
+          <t>-32,31; 7,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 45,93</t>
+          <t>-1,87; 46,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 26,02</t>
+          <t>-15,9; 27,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,6; -2,14</t>
+          <t>-31,59; 0,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 20,51</t>
+          <t>-12,54; 20,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 10,82</t>
+          <t>-19,25; 12,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,57; -2,47</t>
+          <t>-27,11; -2,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 15,46</t>
+          <t>-0,33; 15,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 7,02</t>
+          <t>-7,14; 7,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -2,74</t>
+          <t>-15,99; -2,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,08</t>
+          <t>-9,57; 5,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -5,85</t>
+          <t>-20,19; -5,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-53,75; -18,72</t>
+          <t>-50,8; -18,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,95</t>
+          <t>-4,41; 6,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,35; -2,49</t>
+          <t>-12,87; -2,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-37,02; -13,88</t>
+          <t>-36,22; -14,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 50,48</t>
+          <t>-0,7; 52,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 22,72</t>
+          <t>-18,49; 25,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -8,54</t>
+          <t>-40,66; -8,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 8,63</t>
+          <t>-14,9; 8,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -10,54</t>
+          <t>-31,62; -10,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,77; -30,99</t>
+          <t>-80,29; -31,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 17,51</t>
+          <t>-8,45; 14,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,4; -5,36</t>
+          <t>-25,01; -5,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -29,17</t>
+          <t>-72,69; -29,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 11,57</t>
+          <t>-7,63; 11,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -2,21</t>
+          <t>-18,44; -1,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,31; -5,17</t>
+          <t>-21,86; -5,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 9,27</t>
+          <t>-2,88; 9,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -2,03</t>
+          <t>-15,94; -2,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 2,81</t>
+          <t>-7,68; 2,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 8,07</t>
+          <t>-1,87; 8,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -4,29</t>
+          <t>-14,63; -4,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -1,9</t>
+          <t>-11,28; -2,17</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 18,51</t>
+          <t>-9,89; 18,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -3,46</t>
+          <t>-25,59; -2,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,09; -8,1</t>
+          <t>-29,94; -8,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,01</t>
+          <t>-3,46; 12,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,53; -2,63</t>
+          <t>-19,03; -2,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 3,78</t>
+          <t>-9,16; 3,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,08</t>
+          <t>-2,42; 11,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,25; -5,7</t>
+          <t>-18,86; -6,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -2,79</t>
+          <t>-14,43; -3,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,48</t>
+          <t>-0,18; 3,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,32</t>
+          <t>-1,03; 2,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,72; 24,28</t>
+          <t>0,84; 25,28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,56</t>
+          <t>0,34; 4,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,64</t>
+          <t>-2,45; 1,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,03</t>
+          <t>-6,76; -0,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,68; 3,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,38</t>
+          <t>-1,31; 1,45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 13,18</t>
+          <t>-1,1; 11,53</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 26,39</t>
+          <t>-1,09; 25,29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 17,95</t>
+          <t>-6,91; 18,88</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5,08; 178,12</t>
+          <t>5,74; 192,07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,4; 20,51</t>
+          <t>1,45; 20,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,44</t>
+          <t>-9,98; 6,92</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -0,79</t>
+          <t>-28,14; -0,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,42; 19,11</t>
+          <t>3,23; 18,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,71</t>
+          <t>-6,77; 7,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 72,82</t>
+          <t>-5,77; 63,55</t>
         </is>
       </c>
     </row>
